--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0032.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0032.xlsx
@@ -1885,7 +1885,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Gói Nguyên Liệu Tăng Cấp Weapon Skill Basic</t>
+          <t>Gói Nguyên Liệu Tăng Cấp Vũ khí Skill Basic</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Gói Nguyên Liệu Tăng Cấp Weapon Skill Basic</t>
+          <t>Gói Nguyên Liệu Tăng Cấp Vũ khí Skill Basic</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Gói Material Tăng Cấp Weapon Skill Cao Cấp</t>
+          <t>Gói Material Tăng Cấp Vũ khí Skill Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Gói Material Tăng Cấp Weapon Skill Cao Cấp</t>
+          <t>Gói Material Tăng Cấp Vũ khí Skill Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Giảm 25% Cooldown chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 25% Thời gian hồi chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Giảm 15% Cooldown chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 15 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 15% Thời gian hồi chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 15 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Giảm 15% Cooldown chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 15 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 15% Thời gian hồi chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 15 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Giảm 30% Cooldown chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 30% Thời gian hồi chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Giảm 30% Cooldown chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 30% Thời gian hồi chiêu Kỹ Năng Grapple cho một Resonators đã chọn trong đội trong 30 phút. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mô-đun dữ liệu cho Cube. Equip để giảm Cooldown kỹ năng.</t>
+          <t>Mô-đun dữ liệu cho Cube. Equip để giảm Thời gian hồi kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       <c r="M238" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Jinhsi Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt Core để phóng Chùm Light bắn phá khu vực phía trước trong {2} giây, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonator kích hoạt. Cooldown chiêu: {6} giây.
+Sử dụng Kỹ Năng Cốt Core để phóng Chùm Light bắn phá khu vực phía trước trong {2} giây, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonator kích hoạt. Thời gian hồi chiêu: {6} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Tia Kỹ Năng] [Thời Gian Kỹ Năng]
@@ -16090,10 +16090,10 @@
       <c r="M239" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Changli Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt để thi triển Lửa Hy Sinh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; bằng {1} Tấn Công của Resonators kích hoạt lên các mục tiêu gần đó và tăng Tấn Công cho tất cả Resonators trong đội ở gần thêm {2} trong {3} giây, có thể chồng chất lên đến {5} lần. Cooldown chiêu: {4} giây
+Sử dụng Kỹ Năng Cốt để thi triển Lửa Hy Sinh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; bằng {1} Tấn Công của Resonators kích hoạt lên các mục tiêu gần đó và tăng Tấn Công cho tất cả Resonators trong đội ở gần thêm {2} trong {3} giây, có thể chồng chất lên đến {5} lần. Thời gian hồi chiêu: {4} giây
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Cooldown chiêu kỹ năng] [Phạm vi kỹ năng]
+[Thời gian hồi chiêu kỹ năng] [Phạm vi kỹ năng]
 &lt;size=40&gt;&lt;color=Title&gt;Fun Fact&lt;/color&gt;&lt;/size&gt;
 Ngay từ nhỏ, Changli đã không thể cưỡng lại những viên bi màu sắc mà mọi người đều yêu thích, chỉ vì cảm giác mát lạnh khi chạm vào lòng bàn tay. Dù giờ đây cô có thể tạo ra chúng dễ dàng bằng Khả Năng Điều Khiển Lửa, cô vẫn thường ghé qua quầy bán bi của người bán hàng.</t>
         </is>
@@ -16170,10 +16170,10 @@
       <c r="M240" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Calcharo Cube's ability&lt;/color&gt;&lt;/size&gt;
-Dùng Kỹ Năng Cốt lõi để phóng Messenger Tử Thần gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; bằng {1} Tấn Công của Resonator đang kích hoạt. Cooldown chiêu: {6} giây.
+Dùng Kỹ Năng Cốt lõi để phóng Messenger Tử Thần gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; bằng {1} Tấn Công của Resonator đang kích hoạt. Thời gian hồi chiêu: {6} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Skill Projectiles] [Thời Gian Cooldown]
+[Skill Projectiles] [Thời Gian hồi]
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
 Cấp Skill Projectiles {2}: Tạo thêm {5} Bóng Ma để phóng Messenger Tử Thần gây sát thương bằng {7} sát thương của Messenger Tử Thần từ Calcharo Cube.
@@ -16253,10 +16253,10 @@
       <c r="M241" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Shorekeeper Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt Core để tạo ra Cõi Sao, loại bỏ các hiệu ứng tiêu cực ảnh hưởng đến tất cả Resonators trong phạm vi. Tất cả Cube trong Cõi Sao được hồi phục HP mỗi giây bằng {1} HP tối đa của người sử dụng và tăng Crit. DMG thêm {2}. Hiệu ứng kéo dài {3} giây. Cooldown chiêu: {9} giây.
+Sử dụng Kỹ Năng Cốt Core để tạo ra Cõi Sao, loại bỏ các hiệu ứng tiêu cực ảnh hưởng đến tất cả Resonators trong phạm vi. Tất cả Cube trong Cõi Sao được hồi phục HP mỗi giây bằng {1} HP tối đa của người sử dụng và tăng Crit. DMG thêm {2}. Hiệu ứng kéo dài {3} giây. Thời gian hồi chiêu: {9} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Thời Gian Kỹ Năng] [Thời Gian Cooldown]
+[Thời Gian Kỹ Năng] [Thời Gian hồi]
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enchanced Effect&lt;/color&gt;&lt;/size&gt;
 Cấp Độ Thời Gian Kỹ Năng {4}: Thời gian Cõi Sao tăng thêm {8} giây.
@@ -16333,7 +16333,7 @@
       <c r="M242" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Camellya Cube's ability.&lt;/color&gt;&lt;/size&gt;
-Dùng Kỹ Năng Cốt lõi để thi triển Vũ Điệu Dây Leo tấn công mục tiêu trong phạm vi rộng trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {3} giây.
+Dùng Kỹ Năng Cốt lõi để thi triển Vũ Điệu Dây Leo tấn công mục tiêu trong phạm vi rộng trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator đang kích hoạt. Thời gian hồi chiêu: {3} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Tần Suất Attack] [Skill Range]
@@ -16413,7 +16413,7 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Carlotta Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt để triệu hồi Súng Hỏa Mai bắn vào các mục tiêu gần đó, gây tổng cộng &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; bằng {3} Tấn Công của Resonator kích hoạt. Cooldown chiêu: {8} giây.
+Sử dụng Kỹ Năng Cốt để triệu hồi Súng Hỏa Mai bắn vào các mục tiêu gần đó, gây tổng cộng &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; bằng {3} Tấn Công của Resonator kích hoạt. Thời gian hồi chiêu: {8} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Số đạn kỹ năng] [Thời gian kỹ năng]
@@ -16496,7 +16496,7 @@
       <c r="M244" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Roccia Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt Core để tạo ra Bão Tâm Trí hút các mục tiêu gần đó trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator kích hoạt. Cooldown chiêu: {8} giây.
+Sử dụng Kỹ Năng Cốt Core để tạo ra Bão Tâm Trí hút các mục tiêu gần đó trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator kích hoạt. Thời gian hồi chiêu: {8} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Tần Suất Attack] [Thời Gian Kỹ Năng]
@@ -16579,10 +16579,10 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Brant Cube's ability&lt;/color&gt;&lt;/size&gt;
-Dùng Kỹ Năng Cốt lõi để triệu hồi mỏ neo tấn công, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; bằng {1} Tấn Công của Resonators đang kích hoạt và tạo ra vài Quả Cam Ngon khi chạm đất. Resonators nhặt Quả Cam Ngon sẽ được tăng Tấn Công thêm {7} và phục hồi HP bằng {8} HP tối đa của người sử dụng trong {2} giây, có thể chồng chất lên đến {4} lần. Cooldown chiêu: {6} giây.
+Dùng Kỹ Năng Cốt lõi để triệu hồi mỏ neo tấn công, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; bằng {1} Tấn Công của Resonators đang kích hoạt và tạo ra vài Quả Cam Ngon khi chạm đất. Resonators nhặt Quả Cam Ngon sẽ được tăng Tấn Công thêm {7} và phục hồi HP bằng {8} HP tối đa của người sử dụng trong {2} giây, có thể chồng chất lên đến {4} lần. Thời gian hồi chiêu: {6} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Skill Projectiles] [Thời Gian Cooldown]
+[Skill Projectiles] [Thời Gian hồi]
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
 Cấp Skill Projectiles {3}: Số lượng Quả Cam Ngon tăng thêm {5}.
@@ -16659,10 +16659,10 @@
       <c r="M246" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Cantarella Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt để làm đình trệ mục tiêu trong phạm vi nhất định trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {1} Tấn Công của Resonator kích hoạt. Cooldown chiêu: {3} giây
+Sử dụng Kỹ Năng Cốt để làm đình trệ mục tiêu trong phạm vi nhất định trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {1} Tấn Công của Resonator kích hoạt. Thời gian hồi chiêu: {3} giây
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Cooldown chiêu kỹ năng] [Phạm vi kỹ năng]
+[Thời gian hồi chiêu kỹ năng] [Phạm vi kỹ năng]
 &lt;size=40&gt;&lt;color=Title&gt;Fun Fact&lt;/color&gt;&lt;/size&gt;
 Hiếm ai giấu được bí mật trước Cantarella. Chỉ cần liếc qua, chất độc của cô sẽ tiết lộ tất cả những gì cô cần biết.</t>
         </is>
@@ -16736,10 +16736,10 @@
       <c r="M247" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Zani Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt Core để thực hiện chuỗi tấn công liên tiếp trong {4} giây, mỗi đòn gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {2} Tấn Công của Resonator đang kích hoạt. Cooldown chiêu: {3} giây
+Sử dụng Kỹ Năng Cốt Core để thực hiện chuỗi tấn công liên tiếp trong {4} giây, mỗi đòn gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {2} Tấn Công của Resonator đang kích hoạt. Thời gian hồi chiêu: {3} giây
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
-[Cooldown chiêu kỹ năng] [Phạm vi kỹ năng]
+[Thời gian hồi chiêu kỹ năng] [Phạm vi kỹ năng]
 &lt;size=40&gt;&lt;color=Title&gt;Fun Fact&lt;/color&gt;&lt;/size&gt;
 Tủ đồ của Zani toàn là những bộ đồ giống hệt nhau, nhưng cô ấy luôn biết chính xác bộ nào phù hợp cho từng dịp.</t>
         </is>
@@ -16816,7 +16816,7 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Cartethyia Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt để triệu hồi Kiếm Bão liên tục tấn công mục tiêu trong {5} giây, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonator kích hoạt. Cooldown chiêu: {4} giây
+Sử dụng Kỹ Năng Cốt để triệu hồi Kiếm Bão liên tục tấn công mục tiêu trong {5} giây, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonator kích hoạt. Thời gian hồi chiêu: {4} giây
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Số đạn kỹ năng] [Phạm vi kỹ năng]
@@ -16899,7 +16899,7 @@
       <c r="M249" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Equip to use Phoebe Cube's ability&lt;/color&gt;&lt;/size&gt;
-Sử dụng Kỹ Năng Cốt Core để triệu hồi Light Thần Thánh tấn công liên tục các mục tiêu gần đó, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonators kích hoạt và liên tục tạo Shield cho tất cả Resonators trong đội gần đó dựa trên {9} HP tối đa của người sử dụng. Hiệu ứng kéo dài {2} giây. Cooldown chiêu: {8} giây.
+Sử dụng Kỹ Năng Cốt Core để triệu hồi Light Thần Thánh tấn công liên tục các mục tiêu gần đó, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Tấn Công của Resonators kích hoạt và liên tục tạo Shield cho tất cả Resonators trong đội gần đó dựa trên {9} HP tối đa của người sử dụng. Hiệu ứng kéo dài {2} giây. Thời gian hồi chiêu: {8} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Effective Buffs&lt;/color&gt;&lt;/size&gt;
 [Skill Range] [Thời Gian Kỹ Năng]
@@ -19421,7 +19421,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Giảm 30% Cooldown chiêu Kỹ Năng Echo của một Resonators đã chọn trong đội trong 180 giây. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Giảm 30% Thời gian hồi chiêu Kỹ Năng Echo của một Resonators đã chọn trong đội trong 180 giây. Chỉ có hiệu lực với Resonators của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, tăng Crit. DMG của Basic Attack cho tất cả Resonators trong đội lên 40% trong 15 giây và giảm Cooldown chiêu Resonance Skill của họ đi 10 giây.
+          <t>Sau khi sử dụng Resonance Liberation, tăng Crit. DMG của Basic Attack cho tất cả Resonators trong đội lên 40% trong 15 giây và giảm Thời gian hồi chiêu Resonance Skill của họ đi 10 giây.
 Mã thông báo này có thể sử dụng tối đa &lt;color=#fee388&gt;2&lt;/color&gt; lần tại Whimpering Wastes.</t>
         </is>
       </c>
@@ -23614,7 +23614,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Mỗi lần sử dụng Resonance Skill sẽ giảm 20% Cooldown chiêu của Resonance Liberation và hồi 20% Resonance Energy. Hiệu ứng này có Cooldown chiêu là 3 giây.
+          <t>Mỗi lần sử dụng Resonance Skill sẽ giảm 20% Thời gian hồi chiêu của Resonance Liberation và hồi 20% Resonance Energy. Hiệu ứng này có Thời gian hồi chiêu là 3 giây.
 Mảnh này có thể sử dụng tối đa &lt;color=#fee388&gt;2&lt;/color&gt; lần tại Whimpering Wastes.</t>
         </is>
       </c>
@@ -24797,7 +24797,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, tăng Crit. DMG của Basic Attack cho tất cả thành viên trong đội lên 40% trong 15 giây và giảm Cooldown chiêu Resonance Skill của họ đi 10 giây.</t>
+          <t>Sau khi sử dụng Resonance Liberation, tăng Crit. DMG của Basic Attack cho tất cả thành viên trong đội lên 40% trong 15 giây và giảm Thời gian hồi chiêu Resonance Skill của họ đi 10 giây.</t>
         </is>
       </c>
     </row>
@@ -24862,7 +24862,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Mỗi lần sử dụng Resonance Skill sẽ giảm 20% Cooldown chiêu của Resonance Liberation và hồi 20% Resonance Energy. Hiệu ứng này có Cooldown chiêu là 3 giây.</t>
+          <t>Mỗi lần sử dụng Resonance Skill sẽ giảm 20% Thời gian hồi chiêu của Resonance Liberation và hồi 20% Resonance Energy. Hiệu ứng này có Thời gian hồi chiêu là 3 giây.</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25642,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Beohr Trench</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Hào Beohr</t>
         </is>
       </c>
     </row>
@@ -25707,7 +25707,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Avinoleum - Đất Tàn Dư</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Avinoleum - Đất Tàn Dư</t>
         </is>
       </c>
     </row>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Septimont</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Septimont</t>
         </is>
       </c>
     </row>
@@ -26570,14 +26570,14 @@
       <c r="M396" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {0} Attack của Resonator hiện tại.
+Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {0} ATK của Resonator hiện tại.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Biến thành Khối Jinhsi và phóng Chùm Tia Light quét qua khu vực phía trước trong {2} giây, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator hiện tại. Cooldown chiêu: {6} giây.
-- Khối Jinhsi có thể điều khiển hướng của Chùm Tia Light.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Biến hình thành Khối Jinhsi và phóng Chùm Tia Ánh Sáng quét qua khu vực phía trước trong {2} giây, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; mỗi giây bằng {1} ATK của Resonator hiện tại. Thời gian hồi chiêu: {6} giây.
+- Khối Jinhsi có thể điều khiển hướng của Chùm Tia Ánh Sáng.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Skill Projectiles {4}: Số lượng Chùm Tia Light tăng thêm {5}.
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Nâng Cao&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Đạn Kỹ Năng {4}: Số lượng Chùm Tia Ánh Sáng tăng thêm {5}.
 Cấp Độ Thời Gian Kỹ Năng {3}: Thời gian kỹ năng tăng thêm {9} giây.</t>
         </is>
       </c>
@@ -26648,10 +26648,10 @@
       <c r="M397" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; tương đương {0} Attack của Resonators đang kích hoạt.
+Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tương đương {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Changli Cube kích hoạt Flaming Sacrifice tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; tương đương {1} Attack của Resonators đang kích hoạt và tăng Attack cho tất cả Resonators trong đội gần đó lên {2} trong {3} giây, có thể chồng chất lên đến {5} lần. Cooldown chiêu: {4} giây.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Khối Changli kích hoạt Flaming Sacrifice tấn công mục tiêu, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tương đương {1} ATK của Resonator đang kích hoạt và tăng ATK cho tất cả Resonator trong đội gần đó lên {2} trong {3} giây, có thể chồng chất lên đến {5} lần. Thời gian hồi chiêu: {4} giây.</t>
         </is>
       </c>
     </row>
@@ -26724,13 +26724,13 @@
       <c r="M398" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; tương đương {0} Attack của Resonator đang kích hoạt.
+Gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; tương đương {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Calcharo Cube triệu hồi Messenger Tử Thần tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; tương đương {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {6} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Khối Calcharo triệu hồi Sứ Giả Tử Thần tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; tương đương {1} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {6} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Skill Projectiles {2}: Tạo thêm {5} Hồn Ma để triệu hồi Messenger Tử Thần, gây sát thương bằng {7} sát thương Messenger Tử Thần của Calcharo Cube.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Tăng Cường&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Đạn Kỹ Năng {2}: Tạo thêm {5} Hồn Ma để triệu hồi Sứ Giả Tử Thần, gây DMG bằng {7} DMG Sứ Giả Tử Thần của Khối Calcharo.</t>
         </is>
       </c>
     </row>
@@ -26803,12 +26803,12 @@
       <c r="M399" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {0} Attack của Resonators hiện tại.
+Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {0} ATK của Resonator hiện tại.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Shorekeeper Cube tạo ra Stellarealm, loại bỏ hiệu ứng tiêu cực tác động lên tất cả Resonators trong phạm vi. Tất cả Cube trong Stellarealm được phục hồi HP bằng {1} HP tối đa của người sử dụng mỗi giây và tăng Crit. DMG thêm {2}. Hiệu ứng này kéo dài trong {3} giây. Cooldown chiêu: {9} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Shorekeeper Cube tạo ra Stellarealm, loại bỏ hiệu ứng tiêu cực tác động lên tất cả Resonator trong phạm vi. Tất cả Cube trong Stellarealm được phục hồi HP bằng {1} HP tối đa của người sử dụng mỗi giây và tăng Crit. DMG thêm {2}. Hiệu ứng này kéo dài trong {3} giây. Thời gian hồi chiêu: {9} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Nâng Cao&lt;/color&gt;&lt;/size&gt;
 Cấp Độ Kéo Dài Kỹ Năng {4}: Thời gian Stellarealm tăng thêm {8} giây.</t>
         </is>
       </c>
@@ -26879,10 +26879,10 @@
       <c r="M400" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {0} Attack của Resonator đang kích hoạt.
+Gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; bằng {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Biến thành Camellya Cube và thi triển Vining Waltz tấn công mục tiêu trong phạm vi rộng trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {3} giây.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Biến hình thành Khối Camellya và thi triển Vining Waltz tấn công mục tiêu trong phạm vi rộng trong {2} giây, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; mỗi giây bằng {1} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -26955,13 +26955,13 @@
       <c r="M401" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; bằng {0} Attack của Resonator đang kích hoạt. 
+Gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; bằng {0} ATK của Resonator đang kích hoạt. 
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Carlotta Cube triệu hồi Súng Hỏa Mai bắn vào các mục tiêu gần đó, gây tổng cộng &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; bằng {3} Attack của Resonator đang kích hoạt. Cooldown chiêu: {8} giây
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Carlotta Cube triệu hồi Súng Hỏa Mai bắn vào các mục tiêu gần đó, gây tổng cộng &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; bằng {3} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {8} giây
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Skill Projectiles {4}: Số lượng Súng Hỏa Mai tăng thêm {7}.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Tăng Cường&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Đạn Kỹ Năng {4}: Số lượng Súng Hỏa Mai tăng thêm {7}.</t>
         </is>
       </c>
     </row>
@@ -27034,12 +27034,12 @@
       <c r="M402" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {0} Attack của Resonator đang kích hoạt.
+Gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; bằng {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Roccia tạo ra Mind Storm hút mục tiêu xung quanh vào trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {8} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Roccia tạo ra Mind Storm hút mục tiêu xung quanh vào trong {2} giây, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; mỗi giây bằng {1} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {8} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Nâng Cao&lt;/color&gt;&lt;/size&gt;
 Cấp Độ Thời Gian Kỹ Năng {3}: Thời gian Mind Storm kéo dài thêm {7} giây.</t>
         </is>
       </c>
@@ -27113,13 +27113,13 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; tương đương {0} Attack của Resonators đang kích hoạt.
+Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tương đương {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Brant Cube triệu hồi một mỏ neo tấn công, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; tương đương {1} Attack của Resonators đang kích hoạt và tạo ra vài Quả Cam Tươi khi chạm đất. Resonators nhặt Quả Cam Tươi sẽ được tăng Attack lên {7} và phục hồi HP bằng {8} HP tối đa của người sử dụng trong {2} giây, có thể chồng chất lên đến {4} lần. Cooldown chiêu: {6} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Khối Brant triệu hồi một mỏ neo tấn công, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tương đương {1} ATK của Resonator đang kích hoạt và tạo ra vài Quả Cam Tươi khi chạm đất. Resonator nhặt Quả Cam Tươi sẽ được tăng ATK lên {7} và phục hồi HP bằng {8} HP tối đa của người sử dụng trong {2} giây, có thể chồng chất lên đến {4} lần. Thời gian hồi chiêu: {6} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Skill Projectiles {3}: Số lượng Quả Cam Tươi tăng thêm {5}.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Nâng Cao&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Đạn Kỹ Năng {3}: Số lượng Quả Cam Tươi tăng thêm {5}.</t>
         </is>
       </c>
     </row>
@@ -27189,10 +27189,10 @@
       <c r="M404" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {0} Attack của Resonator đang kích hoạt.
+Gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; bằng {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Biến thành Cantarella Cube và làm đình trệ mục tiêu trong phạm vi nhất định trong {2} giây, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {3} giây.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Biến hình thành Khối Cantarella và làm đình trệ mục tiêu trong phạm vi nhất định trong {2} giây, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; bằng {1} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -27262,10 +27262,10 @@
       <c r="M405" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {0} Attack của Resonator hiện tại và thỉnh thoảng thực hiện tấn công trượt, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {1} Attack của Resonator hiện tại.
+Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {0} ATK của Resonator hiện tại và thỉnh thoảng thực hiện tấn công trượt, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {1} ATK của Resonator hiện tại.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Zani Cube thực hiện các đòn tấn công liên tiếp trong {4} giây, mỗi đòn gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {2} Attack của Resonator hiện tại. Cooldown chiêu: {3} giây.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Zani Cube thực hiện các đòn tấn công liên tiếp trong {4} giây, mỗi đòn gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {2} ATK của Resonator hiện tại. Thời gian hồi chiêu: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -27338,13 +27338,13 @@
       <c r="M406" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; tương đương {0} Attack của Resonator đang kích hoạt.
+Gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; tương đương {0} ATK của Resonator đang kích hoạt.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Cartethyia Cube triệu hồi Kiếm Mưa liên tục tấn công mục tiêu trong {5} giây, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; mỗi giây tương đương {1} Attack của Resonator đang kích hoạt. Cooldown chiêu: {4} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Khối Cartethyia triệu hồi Kiếm Mưa liên tục tấn công mục tiêu trong {5} giây, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; mỗi giây tương đương {1} ATK của Resonator đang kích hoạt. Thời gian hồi chiêu: {4} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Skill Projectiles {2}: Sát thương Kiếm Mưa tăng thêm {6}.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Tăng Cường&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Đạn Kỹ Năng {2}: DMG Kiếm Mưa tăng thêm {6}.</t>
         </is>
       </c>
     </row>
@@ -27417,13 +27417,13 @@
       <c r="M407" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {0} Attack của Resonators hiện tại.
+Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {0} ATK của Resonator hiện tại.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Core Skill&lt;/color&gt;&lt;/size&gt;
-Phoebe Cube thành kính cầu nguyện với Người Bảo Hộ và triệu hồi Light Thần Thánh tấn công liên tục các mục tiêu xung quanh, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; mỗi giây bằng {1} Attack của Resonators hiện tại và liên tục tạo Shield cho tất cả Resonators trong đội gần đó dựa trên {9} HP tối đa của người sử dụng. Hiệu ứng kéo dài {2} giây. Cooldown chiêu: {8} giây.
+&lt;size=40&gt;&lt;color=Title&gt;Kỹ Năng Cốt Lõi&lt;/color&gt;&lt;/size&gt;
+Khối Phoebe thành kính cầu nguyện với Người Bảo Hộ và triệu hồi Ánh Sáng Thần Thánh tấn công liên tục các mục tiêu xung quanh, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; mỗi giây bằng {1} ATK của Resonator hiện tại và liên tục tạo Khiên cho tất cả Resonator trong đội gần đó dựa trên {9} HP tối đa của người sử dụng. Hiệu ứng kéo dài {2} giây. Thời gian hồi chiêu: {8} giây.
 &lt;size=10&gt; &lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Enhanced Effect&lt;/color&gt;&lt;/size&gt;
-Cấp Độ Thời Gian Kỹ Năng {3}: Thời gian Light Thần Thánh tăng thêm {7} giây.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Hiệu Ứng Nâng Cao&lt;/color&gt;&lt;/size&gt;
+Cấp Độ Thời Gian Kỹ Năng {3}: Thời gian Ánh Sáng Thần Thánh tăng thêm {7} giây.</t>
         </is>
       </c>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch tại Lahai-Roi</t>
+          <t>Tiêu diệt kẻ địch ở Lahai-Roi</t>
         </is>
       </c>
     </row>
